--- a/游戏设计王/老虎机数学专题-倍率百搭.xlsx
+++ b/游戏设计王/老虎机数学专题-倍率百搭.xlsx
@@ -458,12 +458,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="5">
+  <numFmts count="6">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="0.0000%"/>
+    <numFmt numFmtId="177" formatCode="0.0000000000%"/>
   </numFmts>
   <fonts count="32">
     <font>
@@ -1162,7 +1163,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1252,6 +1253,11 @@
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="177" applyNumberFormat="1" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="177" applyNumberFormat="1" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="177" applyNumberFormat="1" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -4910,7 +4916,7 @@
         <f>B6*C6*D6</f>
         <v>2</v>
       </c>
-      <c r="C29" s="10">
+      <c r="C29" s="45">
         <f>B29/8000</f>
         <v>0.00025</v>
       </c>
@@ -4918,7 +4924,7 @@
         <f>B17</f>
         <v>50</v>
       </c>
-      <c r="E29" s="10">
+      <c r="E29" s="45">
         <f>C29*D29</f>
         <v>0.0125</v>
       </c>
@@ -4934,7 +4940,7 @@
         <f>B7*C7*D7</f>
         <v>18</v>
       </c>
-      <c r="C30" s="10">
+      <c r="C30" s="45">
         <f>B30/8000</f>
         <v>0.00225</v>
       </c>
@@ -4942,7 +4948,7 @@
         <f>B18</f>
         <v>10</v>
       </c>
-      <c r="E30" s="10">
+      <c r="E30" s="45">
         <f>C30*D30</f>
         <v>0.0225</v>
       </c>
@@ -4958,7 +4964,7 @@
         <f>B8*C8*D8</f>
         <v>64</v>
       </c>
-      <c r="C31" s="10">
+      <c r="C31" s="45">
         <f>B31/8000</f>
         <v>0.008</v>
       </c>
@@ -4966,7 +4972,7 @@
         <f>B19</f>
         <v>5</v>
       </c>
-      <c r="E31" s="10">
+      <c r="E31" s="45">
         <f>C31*D31</f>
         <v>0.04</v>
       </c>
@@ -4982,7 +4988,7 @@
         <f>B9*C9*D9</f>
         <v>144</v>
       </c>
-      <c r="C32" s="10">
+      <c r="C32" s="45">
         <f>B32/8000</f>
         <v>0.018</v>
       </c>
@@ -4990,7 +4996,7 @@
         <f>B20</f>
         <v>3</v>
       </c>
-      <c r="E32" s="10">
+      <c r="E32" s="45">
         <f>C32*D32</f>
         <v>0.054</v>
       </c>
@@ -5006,7 +5012,7 @@
         <f>B10*C10*D10</f>
         <v>150</v>
       </c>
-      <c r="C33" s="10">
+      <c r="C33" s="45">
         <f>B33/8000</f>
         <v>0.01875</v>
       </c>
@@ -5014,7 +5020,7 @@
         <f>B21</f>
         <v>1</v>
       </c>
-      <c r="E33" s="10">
+      <c r="E33" s="45">
         <f>C33*D33</f>
         <v>0.01875</v>
       </c>
@@ -5026,7 +5032,7 @@
       <c r="A34" s="11" t="s">
         <v>98</v>
       </c>
-      <c r="B34" s="12">
+      <c r="B34" s="46">
         <f>SUM(E29:E33)</f>
         <v>0.14775</v>
       </c>
@@ -5151,7 +5157,7 @@
         <f>(B6+B$5)*(C6+C$5)*(D6+D$5)-B29</f>
         <v>16</v>
       </c>
-      <c r="C40" s="10">
+      <c r="C40" s="45">
         <f>B40/8000</f>
         <v>0.002</v>
       </c>
@@ -5159,7 +5165,7 @@
         <f>B17*$B$22</f>
         <v>150</v>
       </c>
-      <c r="E40" s="10">
+      <c r="E40" s="45">
         <f>C40*D40</f>
         <v>0.3</v>
       </c>
@@ -5175,7 +5181,7 @@
         <f>(B7+B$5)*(C7+C$5)*(D7+D$5)-B30</f>
         <v>42</v>
       </c>
-      <c r="C41" s="10">
+      <c r="C41" s="45">
         <f>B41/8000</f>
         <v>0.00525</v>
       </c>
@@ -5183,7 +5189,7 @@
         <f>B18*$B$22</f>
         <v>30</v>
       </c>
-      <c r="E41" s="10">
+      <c r="E41" s="45">
         <f>C41*D41</f>
         <v>0.1575</v>
       </c>
@@ -5199,7 +5205,7 @@
         <f>(B8+B$5)*(C8+C$5)*(D8+D$5)-B31</f>
         <v>80</v>
       </c>
-      <c r="C42" s="10">
+      <c r="C42" s="45">
         <f>B42/8000</f>
         <v>0.01</v>
       </c>
@@ -5207,7 +5213,7 @@
         <f>B19*$B$22</f>
         <v>15</v>
       </c>
-      <c r="E42" s="10">
+      <c r="E42" s="45">
         <f>C42*D42</f>
         <v>0.15</v>
       </c>
@@ -5223,7 +5229,7 @@
         <f>(B9+B$5)*(C9+C$5)*(D9+D$5)-B32</f>
         <v>144</v>
       </c>
-      <c r="C43" s="10">
+      <c r="C43" s="45">
         <f>B43/8000</f>
         <v>0.018</v>
       </c>
@@ -5231,7 +5237,7 @@
         <f>B20*$B$22</f>
         <v>9</v>
       </c>
-      <c r="E43" s="10">
+      <c r="E43" s="45">
         <f>C43*D43</f>
         <v>0.162</v>
       </c>
@@ -5247,7 +5253,7 @@
         <f>(B10+B$5)*(C10+C$5)*(D10+D$5)-B33</f>
         <v>130</v>
       </c>
-      <c r="C44" s="10">
+      <c r="C44" s="45">
         <f>B44/8000</f>
         <v>0.01625</v>
       </c>
@@ -5255,7 +5261,7 @@
         <f>B21*$B$22</f>
         <v>3</v>
       </c>
-      <c r="E44" s="10">
+      <c r="E44" s="45">
         <f>C44*D44</f>
         <v>0.04875</v>
       </c>
@@ -5267,7 +5273,7 @@
       <c r="A45" s="11" t="s">
         <v>98</v>
       </c>
-      <c r="B45" s="12">
+      <c r="B45" s="46">
         <f>SUM(E40:E44)</f>
         <v>0.81825</v>
       </c>
@@ -5575,7 +5581,7 @@
         <f>B6*C6*D6</f>
         <v>2</v>
       </c>
-      <c r="D60" s="10">
+      <c r="D60" s="45">
         <f t="shared" ref="D60:D99" si="0">C60/8000</f>
         <v>0.00025</v>
       </c>
@@ -5583,7 +5589,7 @@
         <f>B17*3^0</f>
         <v>50</v>
       </c>
-      <c r="F60" s="10">
+      <c r="F60" s="45">
         <f t="shared" ref="F60:F99" si="1">D60*E60</f>
         <v>0.0125</v>
       </c>
@@ -5599,7 +5605,7 @@
         <f>B$5*C6*D6</f>
         <v>0</v>
       </c>
-      <c r="D61" s="10">
+      <c r="D61" s="45">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -5607,7 +5613,7 @@
         <f>B17*3^1</f>
         <v>150</v>
       </c>
-      <c r="F61" s="10">
+      <c r="F61" s="45">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -5623,7 +5629,7 @@
         <f>B6*C$5*D6</f>
         <v>4</v>
       </c>
-      <c r="D62" s="10">
+      <c r="D62" s="45">
         <f t="shared" si="0"/>
         <v>0.0005</v>
       </c>
@@ -5631,7 +5637,7 @@
         <f>B17*3^1</f>
         <v>150</v>
       </c>
-      <c r="F62" s="10">
+      <c r="F62" s="45">
         <f t="shared" si="1"/>
         <v>0.075</v>
       </c>
@@ -5647,7 +5653,7 @@
         <f>B$5*C$5*D6</f>
         <v>0</v>
       </c>
-      <c r="D63" s="10">
+      <c r="D63" s="45">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -5655,7 +5661,7 @@
         <f>B17*3^2</f>
         <v>450</v>
       </c>
-      <c r="F63" s="10">
+      <c r="F63" s="45">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -5671,7 +5677,7 @@
         <f>B6*C6*D$5</f>
         <v>4</v>
       </c>
-      <c r="D64" s="10">
+      <c r="D64" s="45">
         <f t="shared" si="0"/>
         <v>0.0005</v>
       </c>
@@ -5679,7 +5685,7 @@
         <f>B17*3^1</f>
         <v>150</v>
       </c>
-      <c r="F64" s="10">
+      <c r="F64" s="45">
         <f t="shared" si="1"/>
         <v>0.075</v>
       </c>
@@ -5695,7 +5701,7 @@
         <f>B$5*C6*D$5</f>
         <v>0</v>
       </c>
-      <c r="D65" s="10">
+      <c r="D65" s="45">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -5703,7 +5709,7 @@
         <f>B17*3^2</f>
         <v>450</v>
       </c>
-      <c r="F65" s="10">
+      <c r="F65" s="45">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -5719,7 +5725,7 @@
         <f>B6*C$5*D$5</f>
         <v>8</v>
       </c>
-      <c r="D66" s="10">
+      <c r="D66" s="45">
         <f t="shared" si="0"/>
         <v>0.001</v>
       </c>
@@ -5727,7 +5733,7 @@
         <f>B17*3^2</f>
         <v>450</v>
       </c>
-      <c r="F66" s="10">
+      <c r="F66" s="45">
         <f t="shared" si="1"/>
         <v>0.45</v>
       </c>
@@ -5743,7 +5749,7 @@
         <f>B$5*C$5*D$5</f>
         <v>0</v>
       </c>
-      <c r="D67" s="10">
+      <c r="D67" s="45">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -5751,7 +5757,7 @@
         <f>B17*3^3</f>
         <v>1350</v>
       </c>
-      <c r="F67" s="10">
+      <c r="F67" s="45">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -5767,7 +5773,7 @@
         <f>B7*C7*D7</f>
         <v>18</v>
       </c>
-      <c r="D68" s="10">
+      <c r="D68" s="45">
         <f t="shared" si="0"/>
         <v>0.00225</v>
       </c>
@@ -5775,7 +5781,7 @@
         <f>B18*3^0</f>
         <v>10</v>
       </c>
-      <c r="F68" s="10">
+      <c r="F68" s="45">
         <f t="shared" si="1"/>
         <v>0.0225</v>
       </c>
@@ -5791,7 +5797,7 @@
         <f>B$5*C7*D7</f>
         <v>0</v>
       </c>
-      <c r="D69" s="10">
+      <c r="D69" s="45">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -5799,7 +5805,7 @@
         <f>B18*3^1</f>
         <v>30</v>
       </c>
-      <c r="F69" s="10">
+      <c r="F69" s="45">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -5815,7 +5821,7 @@
         <f>B7*C$5*D7</f>
         <v>12</v>
       </c>
-      <c r="D70" s="10">
+      <c r="D70" s="45">
         <f t="shared" si="0"/>
         <v>0.0015</v>
       </c>
@@ -5823,7 +5829,7 @@
         <f>B18*3^1</f>
         <v>30</v>
       </c>
-      <c r="F70" s="10">
+      <c r="F70" s="45">
         <f t="shared" si="1"/>
         <v>0.045</v>
       </c>
@@ -5839,7 +5845,7 @@
         <f>B$5*C$5*D7</f>
         <v>0</v>
       </c>
-      <c r="D71" s="10">
+      <c r="D71" s="45">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -5847,7 +5853,7 @@
         <f>B18*3^2</f>
         <v>90</v>
       </c>
-      <c r="F71" s="10">
+      <c r="F71" s="45">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -5863,7 +5869,7 @@
         <f>B7*C7*D$5</f>
         <v>18</v>
       </c>
-      <c r="D72" s="10">
+      <c r="D72" s="45">
         <f t="shared" si="0"/>
         <v>0.00225</v>
       </c>
@@ -5871,7 +5877,7 @@
         <f>B18*3^1</f>
         <v>30</v>
       </c>
-      <c r="F72" s="10">
+      <c r="F72" s="45">
         <f t="shared" si="1"/>
         <v>0.0675</v>
       </c>
@@ -5887,7 +5893,7 @@
         <f>B$5*C7*D$5</f>
         <v>0</v>
       </c>
-      <c r="D73" s="10">
+      <c r="D73" s="45">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -5895,7 +5901,7 @@
         <f>B18*3^2</f>
         <v>90</v>
       </c>
-      <c r="F73" s="10">
+      <c r="F73" s="45">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -5911,7 +5917,7 @@
         <f>B7*C$5*D$5</f>
         <v>12</v>
       </c>
-      <c r="D74" s="10">
+      <c r="D74" s="45">
         <f t="shared" si="0"/>
         <v>0.0015</v>
       </c>
@@ -5919,7 +5925,7 @@
         <f>B18*3^2</f>
         <v>90</v>
       </c>
-      <c r="F74" s="10">
+      <c r="F74" s="45">
         <f t="shared" si="1"/>
         <v>0.135</v>
       </c>
@@ -5935,7 +5941,7 @@
         <f>B$5*C$5*D$5</f>
         <v>0</v>
       </c>
-      <c r="D75" s="10">
+      <c r="D75" s="45">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -5943,7 +5949,7 @@
         <f>B18*3^3</f>
         <v>270</v>
       </c>
-      <c r="F75" s="10">
+      <c r="F75" s="45">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -5959,7 +5965,7 @@
         <f>B8*C8*D8</f>
         <v>64</v>
       </c>
-      <c r="D76" s="10">
+      <c r="D76" s="45">
         <f t="shared" si="0"/>
         <v>0.008</v>
       </c>
@@ -5967,7 +5973,7 @@
         <f>B19*3^0</f>
         <v>5</v>
       </c>
-      <c r="F76" s="10">
+      <c r="F76" s="45">
         <f t="shared" si="1"/>
         <v>0.04</v>
       </c>
@@ -5983,7 +5989,7 @@
         <f>B$5*C8*D8</f>
         <v>0</v>
       </c>
-      <c r="D77" s="10">
+      <c r="D77" s="45">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -5991,7 +5997,7 @@
         <f>B19*3^1</f>
         <v>15</v>
       </c>
-      <c r="F77" s="10">
+      <c r="F77" s="45">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -6007,7 +6013,7 @@
         <f>B8*C$5*D8</f>
         <v>32</v>
       </c>
-      <c r="D78" s="10">
+      <c r="D78" s="45">
         <f t="shared" si="0"/>
         <v>0.004</v>
       </c>
@@ -6015,7 +6021,7 @@
         <f>B19*3^1</f>
         <v>15</v>
       </c>
-      <c r="F78" s="10">
+      <c r="F78" s="45">
         <f t="shared" si="1"/>
         <v>0.06</v>
       </c>
@@ -6031,7 +6037,7 @@
         <f>B$5*C$5*D8</f>
         <v>0</v>
       </c>
-      <c r="D79" s="10">
+      <c r="D79" s="45">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -6039,7 +6045,7 @@
         <f>B19*3^2</f>
         <v>45</v>
       </c>
-      <c r="F79" s="10">
+      <c r="F79" s="45">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -6055,7 +6061,7 @@
         <f>B8*C8*D$5</f>
         <v>32</v>
       </c>
-      <c r="D80" s="10">
+      <c r="D80" s="45">
         <f t="shared" si="0"/>
         <v>0.004</v>
       </c>
@@ -6063,7 +6069,7 @@
         <f>B19*3^1</f>
         <v>15</v>
       </c>
-      <c r="F80" s="10">
+      <c r="F80" s="45">
         <f t="shared" si="1"/>
         <v>0.06</v>
       </c>
@@ -6079,7 +6085,7 @@
         <f>B$5*C8*D$5</f>
         <v>0</v>
       </c>
-      <c r="D81" s="10">
+      <c r="D81" s="45">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -6087,7 +6093,7 @@
         <f>B19*3^2</f>
         <v>45</v>
       </c>
-      <c r="F81" s="10">
+      <c r="F81" s="45">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -6103,7 +6109,7 @@
         <f>B8*C$5*D$5</f>
         <v>16</v>
       </c>
-      <c r="D82" s="10">
+      <c r="D82" s="45">
         <f t="shared" si="0"/>
         <v>0.002</v>
       </c>
@@ -6111,7 +6117,7 @@
         <f>B19*3^2</f>
         <v>45</v>
       </c>
-      <c r="F82" s="10">
+      <c r="F82" s="45">
         <f t="shared" si="1"/>
         <v>0.09</v>
       </c>
@@ -6127,7 +6133,7 @@
         <f>B$5*C$5*D$5</f>
         <v>0</v>
       </c>
-      <c r="D83" s="10">
+      <c r="D83" s="45">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -6135,7 +6141,7 @@
         <f>B19*3^3</f>
         <v>135</v>
       </c>
-      <c r="F83" s="10">
+      <c r="F83" s="45">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -6151,7 +6157,7 @@
         <f>B9*C9*D9</f>
         <v>144</v>
       </c>
-      <c r="D84" s="10">
+      <c r="D84" s="45">
         <f t="shared" si="0"/>
         <v>0.018</v>
       </c>
@@ -6159,7 +6165,7 @@
         <f>B20*3^0</f>
         <v>3</v>
       </c>
-      <c r="F84" s="10">
+      <c r="F84" s="45">
         <f t="shared" si="1"/>
         <v>0.054</v>
       </c>
@@ -6175,7 +6181,7 @@
         <f>B$5*C9*D9</f>
         <v>0</v>
       </c>
-      <c r="D85" s="10">
+      <c r="D85" s="45">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -6183,7 +6189,7 @@
         <f>B20*3^1</f>
         <v>9</v>
       </c>
-      <c r="F85" s="10">
+      <c r="F85" s="45">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -6199,7 +6205,7 @@
         <f>B9*C$5*D9</f>
         <v>72</v>
       </c>
-      <c r="D86" s="10">
+      <c r="D86" s="45">
         <f t="shared" si="0"/>
         <v>0.009</v>
       </c>
@@ -6207,7 +6213,7 @@
         <f>B20*3^1</f>
         <v>9</v>
       </c>
-      <c r="F86" s="10">
+      <c r="F86" s="45">
         <f t="shared" si="1"/>
         <v>0.081</v>
       </c>
@@ -6223,7 +6229,7 @@
         <f>B$5*C$5*D9</f>
         <v>0</v>
       </c>
-      <c r="D87" s="10">
+      <c r="D87" s="45">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -6231,7 +6237,7 @@
         <f>B20*3^2</f>
         <v>27</v>
       </c>
-      <c r="F87" s="10">
+      <c r="F87" s="45">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -6247,7 +6253,7 @@
         <f>B9*C9*D$5</f>
         <v>48</v>
       </c>
-      <c r="D88" s="10">
+      <c r="D88" s="45">
         <f t="shared" si="0"/>
         <v>0.006</v>
       </c>
@@ -6255,7 +6261,7 @@
         <f>B20*3^1</f>
         <v>9</v>
       </c>
-      <c r="F88" s="10">
+      <c r="F88" s="45">
         <f t="shared" si="1"/>
         <v>0.054</v>
       </c>
@@ -6271,7 +6277,7 @@
         <f>B$5*C9*D$5</f>
         <v>0</v>
       </c>
-      <c r="D89" s="10">
+      <c r="D89" s="45">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -6279,7 +6285,7 @@
         <f>B20*3^2</f>
         <v>27</v>
       </c>
-      <c r="F89" s="10">
+      <c r="F89" s="45">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -6295,7 +6301,7 @@
         <f>B9*C$5*D$5</f>
         <v>24</v>
       </c>
-      <c r="D90" s="10">
+      <c r="D90" s="45">
         <f t="shared" si="0"/>
         <v>0.003</v>
       </c>
@@ -6303,7 +6309,7 @@
         <f>B20*3^2</f>
         <v>27</v>
       </c>
-      <c r="F90" s="10">
+      <c r="F90" s="45">
         <f t="shared" si="1"/>
         <v>0.081</v>
       </c>
@@ -6319,7 +6325,7 @@
         <f>B$5*C$5*D$5</f>
         <v>0</v>
       </c>
-      <c r="D91" s="10">
+      <c r="D91" s="45">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -6327,7 +6333,7 @@
         <f>B20*3^3</f>
         <v>81</v>
       </c>
-      <c r="F91" s="10">
+      <c r="F91" s="45">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -6343,7 +6349,7 @@
         <f>B10*C10*D10</f>
         <v>150</v>
       </c>
-      <c r="D92" s="10">
+      <c r="D92" s="45">
         <f t="shared" si="0"/>
         <v>0.01875</v>
       </c>
@@ -6351,7 +6357,7 @@
         <f>B21*3^0</f>
         <v>1</v>
       </c>
-      <c r="F92" s="10">
+      <c r="F92" s="45">
         <f t="shared" si="1"/>
         <v>0.01875</v>
       </c>
@@ -6367,7 +6373,7 @@
         <f>B$5*C10*D10</f>
         <v>0</v>
       </c>
-      <c r="D93" s="10">
+      <c r="D93" s="45">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -6375,7 +6381,7 @@
         <f>B21*3^1</f>
         <v>3</v>
       </c>
-      <c r="F93" s="10">
+      <c r="F93" s="45">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -6391,7 +6397,7 @@
         <f>B10*C$5*D10</f>
         <v>50</v>
       </c>
-      <c r="D94" s="10">
+      <c r="D94" s="45">
         <f t="shared" si="0"/>
         <v>0.00625</v>
       </c>
@@ -6399,7 +6405,7 @@
         <f>B21*3^1</f>
         <v>3</v>
       </c>
-      <c r="F94" s="10">
+      <c r="F94" s="45">
         <f t="shared" si="1"/>
         <v>0.01875</v>
       </c>
@@ -6415,7 +6421,7 @@
         <f>B$5*C$5*D10</f>
         <v>0</v>
       </c>
-      <c r="D95" s="10">
+      <c r="D95" s="45">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -6423,7 +6429,7 @@
         <f>B21*3^2</f>
         <v>9</v>
       </c>
-      <c r="F95" s="10">
+      <c r="F95" s="45">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -6439,7 +6445,7 @@
         <f>B10*C10*D$5</f>
         <v>60</v>
       </c>
-      <c r="D96" s="10">
+      <c r="D96" s="45">
         <f t="shared" si="0"/>
         <v>0.0075</v>
       </c>
@@ -6447,7 +6453,7 @@
         <f>B21*3^1</f>
         <v>3</v>
       </c>
-      <c r="F96" s="10">
+      <c r="F96" s="45">
         <f t="shared" si="1"/>
         <v>0.0225</v>
       </c>
@@ -6463,7 +6469,7 @@
         <f>B$5*C10*D$5</f>
         <v>0</v>
       </c>
-      <c r="D97" s="10">
+      <c r="D97" s="45">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -6471,7 +6477,7 @@
         <f>B21*3^2</f>
         <v>9</v>
       </c>
-      <c r="F97" s="10">
+      <c r="F97" s="45">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -6487,7 +6493,7 @@
         <f>B10*C$5*D$5</f>
         <v>20</v>
       </c>
-      <c r="D98" s="10">
+      <c r="D98" s="45">
         <f t="shared" si="0"/>
         <v>0.0025</v>
       </c>
@@ -6495,7 +6501,7 @@
         <f>B21*3^2</f>
         <v>9</v>
       </c>
-      <c r="F98" s="10">
+      <c r="F98" s="45">
         <f t="shared" si="1"/>
         <v>0.0225</v>
       </c>
@@ -6511,7 +6517,7 @@
         <f>B$5*C$5*D$5</f>
         <v>0</v>
       </c>
-      <c r="D99" s="10">
+      <c r="D99" s="45">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -6519,7 +6525,7 @@
         <f>B21*3^3</f>
         <v>27</v>
       </c>
-      <c r="F99" s="10">
+      <c r="F99" s="45">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -6540,7 +6546,7 @@
       <c r="E100" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="F100" s="12">
+      <c r="F100" s="46">
         <f>SUM(F60:F99)</f>
         <v>1.485</v>
       </c>
@@ -6629,7 +6635,7 @@
       <c r="A105" s="5" t="s">
         <v>125</v>
       </c>
-      <c r="B105" s="13">
+      <c r="B105" s="47">
         <f>B34</f>
         <v>0.14775</v>
       </c>
@@ -6650,7 +6656,7 @@
       <c r="A106" s="4" t="s">
         <v>126</v>
       </c>
-      <c r="B106" s="10">
+      <c r="B106" s="45">
         <f>B45</f>
         <v>0.81825</v>
       </c>
@@ -6671,7 +6677,7 @@
       <c r="A107" s="11" t="s">
         <v>127</v>
       </c>
-      <c r="B107" s="12">
+      <c r="B107" s="46">
         <f>B105+B106</f>
         <v>0.966</v>
       </c>
@@ -6712,7 +6718,7 @@
       <c r="A109" s="4" t="s">
         <v>129</v>
       </c>
-      <c r="B109" s="10">
+      <c r="B109" s="45">
         <f>F100</f>
         <v>1.485</v>
       </c>
